--- a/Df_medie_chem.xlsx
+++ b/Df_medie_chem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="chem_media" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="125">
   <si>
     <t>Micro</t>
   </si>
@@ -319,6 +319,96 @@
   </si>
   <si>
     <t>AC2</t>
+  </si>
+  <si>
+    <t>Micro_ext</t>
+  </si>
+  <si>
+    <t>NT</t>
+  </si>
+  <si>
+    <t>Go + As</t>
+  </si>
+  <si>
+    <t>Cz + As</t>
+  </si>
+  <si>
+    <t>Cz + Go</t>
+  </si>
+  <si>
+    <t>Cz + Go + As</t>
+  </si>
+  <si>
+    <t>Hu + As</t>
+  </si>
+  <si>
+    <t>Hu + Go</t>
+  </si>
+  <si>
+    <t>Hu + Go + As</t>
+  </si>
+  <si>
+    <t>Mp + As</t>
+  </si>
+  <si>
+    <t>Mp + Go</t>
+  </si>
+  <si>
+    <t>Mp + Go + As</t>
+  </si>
+  <si>
+    <t>Po + As</t>
+  </si>
+  <si>
+    <t>Po + Go</t>
+  </si>
+  <si>
+    <t>Po + Go + As</t>
+  </si>
+  <si>
+    <t>Pt + As</t>
+  </si>
+  <si>
+    <t>Pt + Go</t>
+  </si>
+  <si>
+    <t>Pt + Go + As</t>
+  </si>
+  <si>
+    <t>Sv + As</t>
+  </si>
+  <si>
+    <t>Sv + Go</t>
+  </si>
+  <si>
+    <t>Sv + Go + As</t>
+  </si>
+  <si>
+    <t>Td + As</t>
+  </si>
+  <si>
+    <t>Td + Go</t>
+  </si>
+  <si>
+    <t>Td + Go + As</t>
+  </si>
+  <si>
+    <t>Zb + As</t>
+  </si>
+  <si>
+    <t>Zb + Go</t>
+  </si>
+  <si>
+    <t>Zb + Go + As</t>
+  </si>
+  <si>
+    <t>Zh + As</t>
+  </si>
+  <si>
+    <t>Zh + Go</t>
+  </si>
+  <si>
+    <t>Zh + Go + As</t>
   </si>
 </sst>
 </file>
@@ -2541,141 +2631,145 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>67</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>68</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>69</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>70</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>71</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>72</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>73</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="2">
         <v>1.666666666666667E-3</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>0.37666666666666659</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>221.4</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <f>B2^2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <f>C2^2</f>
         <v>2.7777777777777788E-6</v>
       </c>
-      <c r="I2" s="2">
-        <f t="shared" ref="I2:K2" si="0">C2^2</f>
+      <c r="J2" s="2">
+        <f t="shared" ref="J2:L2" si="0">D2^2</f>
         <v>0.14187777777777771</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="2">
         <f t="shared" si="0"/>
         <v>49017.96</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <f t="shared" si="0"/>
         <v>1.1111111111111111E-3</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>2.004666666666667</v>
       </c>
-      <c r="M2" s="2">
-        <f>L2^2</f>
+      <c r="N2" s="2">
+        <f>M2^2</f>
         <v>4.0186884444444457</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
       <c r="O2">
         <v>0</v>
       </c>
@@ -2706,58 +2800,61 @@
       <c r="X2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2">
         <v>1.3583333333333329</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>0.56499999999999995</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>182.9</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>0.72499999999999998</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>39.583333333333343</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>38.99</v>
       </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H41" si="1">B3^2</f>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I41" si="1">C3^2</f>
         <v>1.8450694444444433</v>
       </c>
-      <c r="I3" s="2">
-        <f t="shared" ref="I3:I41" si="2">C3^2</f>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3:J41" si="2">D3^2</f>
         <v>0.31922499999999993</v>
       </c>
-      <c r="J3" s="2">
-        <f t="shared" ref="J3:J41" si="3">D3^2</f>
+      <c r="K3" s="2">
+        <f t="shared" ref="K3:K41" si="3">E3^2</f>
         <v>33452.410000000003</v>
       </c>
-      <c r="K3" s="2">
-        <f t="shared" ref="K3:K41" si="4">E3^2</f>
+      <c r="L3" s="2">
+        <f t="shared" ref="L3:L41" si="4">F3^2</f>
         <v>0.52562500000000001</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>3.254666666666667</v>
       </c>
-      <c r="M3" s="2">
-        <f t="shared" ref="M3:M41" si="5">L3^2</f>
+      <c r="N3" s="2">
+        <f t="shared" ref="N3:N41" si="5">M3^2</f>
         <v>10.592855111111113</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
         <v>0</v>
       </c>
@@ -2785,64 +2882,67 @@
       <c r="X3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="2">
         <v>3.333333333333334E-3</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>0.26833333333333331</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>199.15</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>0.34666666666666668</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>16.18055555555555</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>23.72</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <f t="shared" si="1"/>
         <v>1.1111111111111115E-5</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <f t="shared" si="2"/>
         <v>7.2002777777777763E-2</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <f t="shared" si="3"/>
         <v>39660.722500000003</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <f t="shared" si="4"/>
         <v>0.12017777777777779</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2.3210000000000002</v>
       </c>
-      <c r="M4" s="2">
+      <c r="N4" s="2">
         <f t="shared" si="5"/>
         <v>5.3870410000000009</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>1</v>
       </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
       <c r="R4">
         <v>0</v>
       </c>
@@ -2864,64 +2964,67 @@
       <c r="X4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="2">
         <v>1.02</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>2.6983333333333328</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>155.23333333333329</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>1.5149999999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>44.097222222222221</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>41.61</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <f t="shared" si="1"/>
         <v>1.0404</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <f t="shared" si="2"/>
         <v>7.2810027777777746</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <f t="shared" si="3"/>
         <v>24097.387777777763</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <f t="shared" si="4"/>
         <v>2.2952249999999998</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>5.6394000000000002</v>
       </c>
-      <c r="M5" s="2">
+      <c r="N5" s="2">
         <f t="shared" si="5"/>
         <v>31.802832360000004</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>1</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
       <c r="R5">
         <v>0</v>
       </c>
@@ -2943,64 +3046,67 @@
       <c r="X5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="2">
         <v>1.865</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>3.4833333333333329</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>134.4</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>0.89</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>49.791666666666671</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>44.88</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f t="shared" si="1"/>
         <v>3.4782250000000001</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <f t="shared" si="2"/>
         <v>12.133611111111108</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <f t="shared" si="3"/>
         <v>18063.36</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="2">
         <f t="shared" si="4"/>
         <v>0.79210000000000003</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>6.6719999999999997</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <f t="shared" si="5"/>
         <v>44.515583999999997</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>1</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
       <c r="R6">
         <v>0</v>
       </c>
@@ -3022,64 +3128,67 @@
       <c r="X6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="2">
         <v>2.5733333333333328</v>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
         <v>4.2350000000000003</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>147.56666666666669</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>54.513888888888893</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>47.59</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="1"/>
         <v>6.622044444444442</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <f t="shared" si="2"/>
         <v>17.935225000000003</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <f t="shared" si="3"/>
         <v>21775.921111111118</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <f t="shared" si="4"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>6.5998333333333337</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <f t="shared" si="5"/>
         <v>43.55780002777778</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>1</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
       <c r="R7">
         <v>0</v>
       </c>
@@ -3101,61 +3210,64 @@
       <c r="X7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2">
         <v>1.34</v>
       </c>
-      <c r="C8" s="2">
+      <c r="D8" s="2">
         <v>0.54333333333333333</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>181.68333333333331</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>1.031666666666667</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>40.972222222222221</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <v>39.799999999999997</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="1"/>
         <v>1.7956000000000003</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <f t="shared" si="2"/>
         <v>0.29521111111111109</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <f t="shared" si="3"/>
         <v>33008.833611111106</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <f t="shared" si="4"/>
         <v>1.0643361111111116</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>3.0950000000000002</v>
       </c>
-      <c r="M8" s="2">
+      <c r="N8" s="2">
         <f t="shared" si="5"/>
         <v>9.5790250000000015</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
       <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>1</v>
       </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
       <c r="Q8">
         <v>0</v>
       </c>
@@ -3180,60 +3292,63 @@
       <c r="X8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="2">
         <v>1.2350000000000001</v>
       </c>
-      <c r="C9" s="2">
+      <c r="D9" s="2">
         <v>0.46666666666666667</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>186.4666666666667</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>0.77500000000000002</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>36.597222222222221</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="2">
         <v>37.229999999999997</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <f t="shared" si="1"/>
         <v>1.5252250000000003</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <f t="shared" si="2"/>
         <v>0.21777777777777779</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <f t="shared" si="3"/>
         <v>34769.817777777789</v>
       </c>
-      <c r="K9" s="2">
+      <c r="L9" s="2">
         <f t="shared" si="4"/>
         <v>0.60062500000000008</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>3.0558333333333332</v>
       </c>
-      <c r="M9" s="2">
+      <c r="N9" s="2">
         <f t="shared" si="5"/>
         <v>9.3381173611111095</v>
       </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
       <c r="O9">
         <v>1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -3259,55 +3374,58 @@
       <c r="X9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="2">
         <v>1.3666666666666669</v>
       </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
         <v>1.9716666666666669</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>147.55000000000001</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>1.658333333333333</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>59.583333333333343</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>50.53</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <f t="shared" si="1"/>
         <v>1.8677777777777784</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <f t="shared" si="2"/>
         <v>3.8874694444444455</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <f t="shared" si="3"/>
         <v>21771.002500000002</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <f t="shared" si="4"/>
         <v>2.7500694444444433</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>4.2358333333333338</v>
       </c>
-      <c r="M10" s="2">
+      <c r="N10" s="2">
         <f t="shared" si="5"/>
         <v>17.942284027777781</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
       <c r="O10">
         <v>0</v>
       </c>
@@ -3315,11 +3433,11 @@
         <v>0</v>
       </c>
       <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
         <v>1</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
       <c r="S10">
         <v>0</v>
       </c>
@@ -3338,55 +3456,58 @@
       <c r="X10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="2">
         <v>2.7866666666666671</v>
       </c>
-      <c r="C11" s="2">
+      <c r="D11" s="2">
         <v>4.7450000000000001</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>123.43333333333329</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>1.405</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <v>63.263888888888893</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="2">
         <v>52.69</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <f t="shared" si="1"/>
         <v>7.7655111111111133</v>
       </c>
-      <c r="I11" s="2">
+      <c r="J11" s="2">
         <f t="shared" si="2"/>
         <v>22.515025000000001</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <f t="shared" si="3"/>
         <v>15235.787777777768</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <f t="shared" si="4"/>
         <v>1.9740250000000001</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>7.6444999999999999</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <f t="shared" si="5"/>
         <v>58.438380249999994</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
       <c r="O11">
         <v>0</v>
       </c>
@@ -3394,11 +3515,11 @@
         <v>0</v>
       </c>
       <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
         <v>1</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
       <c r="S11">
         <v>0</v>
       </c>
@@ -3417,55 +3538,58 @@
       <c r="X11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="2">
         <v>4.3083333333333336</v>
       </c>
-      <c r="C12" s="2">
+      <c r="D12" s="2">
         <v>4.7616666666666667</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>114.48333333333331</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="2">
         <v>1.5866666666666669</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>67.5</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>55.24</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <f t="shared" si="1"/>
         <v>18.561736111111113</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <f t="shared" si="2"/>
         <v>22.673469444444446</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <f t="shared" si="3"/>
         <v>13106.433611111104</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <f t="shared" si="4"/>
         <v>2.5175111111111117</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>9.0151666666666657</v>
       </c>
-      <c r="M12" s="2">
+      <c r="N12" s="2">
         <f t="shared" si="5"/>
         <v>81.273230027777757</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
       <c r="O12">
         <v>0</v>
       </c>
@@ -3473,11 +3597,11 @@
         <v>0</v>
       </c>
       <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
         <v>1</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
       <c r="S12">
         <v>0</v>
       </c>
@@ -3496,55 +3620,58 @@
       <c r="X12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="2">
         <v>3.121666666666667</v>
       </c>
-      <c r="C13" s="2">
+      <c r="D13" s="2">
         <v>5.0983333333333336</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>126.05</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="2">
         <v>0.89166666666666661</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>68.75</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <v>56.01</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <f t="shared" si="1"/>
         <v>9.7448027777777799</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <f t="shared" si="2"/>
         <v>25.993002777777779</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <f t="shared" si="3"/>
         <v>15888.602499999999</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <f t="shared" si="4"/>
         <v>0.79506944444444438</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>8.2948333333333331</v>
       </c>
-      <c r="M13" s="2">
+      <c r="N13" s="2">
         <f t="shared" si="5"/>
         <v>68.804260027777772</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
       <c r="O13">
         <v>0</v>
       </c>
@@ -3552,11 +3679,11 @@
         <v>0</v>
       </c>
       <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>1</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
       <c r="S13">
         <v>0</v>
       </c>
@@ -3575,55 +3702,58 @@
       <c r="X13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="2">
         <v>1.666666666666667E-3</v>
       </c>
-      <c r="C14" s="2">
+      <c r="D14" s="2">
         <v>0.2466666666666667</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>185.2</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="2">
         <v>0.69333333333333336</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>18.611111111111111</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <v>25.56</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <f t="shared" si="1"/>
         <v>2.7777777777777788E-6</v>
       </c>
-      <c r="I14" s="2">
+      <c r="J14" s="2">
         <f t="shared" si="2"/>
         <v>6.0844444444444458E-2</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <f t="shared" si="3"/>
         <v>34299.039999999994</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <f t="shared" si="4"/>
         <v>0.48071111111111114</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M14" s="2">
+      <c r="N14" s="2">
         <f t="shared" si="5"/>
         <v>4.8400000000000007</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
       <c r="O14">
         <v>0</v>
       </c>
@@ -3634,11 +3764,11 @@
         <v>0</v>
       </c>
       <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>1</v>
       </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
       <c r="T14">
         <v>0</v>
       </c>
@@ -3654,55 +3784,58 @@
       <c r="X14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="2">
         <v>2.105</v>
       </c>
-      <c r="C15" s="2">
+      <c r="D15" s="2">
         <v>4.0949999999999998</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>137.0333333333333</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
         <v>1.1233333333333331</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <v>50.972222222222221</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <v>45.56</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <f t="shared" si="1"/>
         <v>4.431025</v>
       </c>
-      <c r="I15" s="2">
+      <c r="J15" s="2">
         <f t="shared" si="2"/>
         <v>16.769024999999999</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <f t="shared" si="3"/>
         <v>18778.134444444437</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="2">
         <f t="shared" si="4"/>
         <v>1.2618777777777772</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>6.6711666666666671</v>
       </c>
-      <c r="M15" s="2">
+      <c r="N15" s="2">
         <f t="shared" si="5"/>
         <v>44.504464694444451</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
       <c r="O15">
         <v>0</v>
       </c>
@@ -3713,11 +3846,11 @@
         <v>0</v>
       </c>
       <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>1</v>
       </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
       <c r="T15">
         <v>0</v>
       </c>
@@ -3733,55 +3866,58 @@
       <c r="X15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="2">
         <v>1.8566666666666669</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
         <v>3.8666666666666671</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>132</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>1.48</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="2">
         <v>58.958333333333343</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="2">
         <v>50.16</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <f t="shared" si="1"/>
         <v>3.4472111111111121</v>
       </c>
-      <c r="I16" s="2">
+      <c r="J16" s="2">
         <f t="shared" si="2"/>
         <v>14.951111111111114</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="2">
         <f t="shared" si="3"/>
         <v>17424</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="2">
         <f t="shared" si="4"/>
         <v>2.1903999999999999</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>6.1544999999999996</v>
       </c>
-      <c r="M16" s="2">
+      <c r="N16" s="2">
         <f t="shared" si="5"/>
         <v>37.877870249999994</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
       <c r="O16">
         <v>0</v>
       </c>
@@ -3792,11 +3928,11 @@
         <v>0</v>
       </c>
       <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>1</v>
       </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
       <c r="T16">
         <v>0</v>
       </c>
@@ -3812,55 +3948,58 @@
       <c r="X16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="2">
         <v>1.611666666666667</v>
       </c>
-      <c r="C17" s="2">
+      <c r="D17" s="2">
         <v>4.1383333333333336</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="2">
         <v>164.16666666666671</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="2">
         <v>0.44166666666666671</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <v>51.597222222222221</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <v>45.92</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <f t="shared" si="1"/>
         <v>2.5974694444444455</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="2">
         <f t="shared" si="2"/>
         <v>17.125802777777782</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <f t="shared" si="3"/>
         <v>26950.69444444446</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <f t="shared" si="4"/>
         <v>0.19506944444444449</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>5.1558333333333328</v>
       </c>
-      <c r="M17" s="2">
+      <c r="N17" s="2">
         <f t="shared" si="5"/>
         <v>26.582617361111105</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
       <c r="O17">
         <v>0</v>
       </c>
@@ -3871,11 +4010,11 @@
         <v>0</v>
       </c>
       <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>1</v>
       </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
       <c r="T17">
         <v>0</v>
       </c>
@@ -3891,55 +4030,58 @@
       <c r="X17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2">
         <v>0.01</v>
       </c>
-      <c r="C18" s="2">
+      <c r="D18" s="2">
         <v>0.64166666666666661</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>160.66666666666671</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>0.1516666666666667</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>42.361111111111107</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>40.61</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <f t="shared" si="2"/>
         <v>0.41173611111111103</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <f t="shared" si="3"/>
         <v>25813.777777777792</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <f t="shared" si="4"/>
         <v>2.3002777777777789E-2</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>2.036</v>
       </c>
-      <c r="M18" s="2">
+      <c r="N18" s="2">
         <f t="shared" si="5"/>
         <v>4.1452960000000001</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
       <c r="O18">
         <v>0</v>
       </c>
@@ -3953,11 +4095,11 @@
         <v>0</v>
       </c>
       <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
         <v>1</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
         <v>0</v>
       </c>
@@ -3970,55 +4112,58 @@
       <c r="X18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="2">
         <v>0.44833333333333342</v>
       </c>
-      <c r="C19" s="2">
+      <c r="D19" s="2">
         <v>2.11</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>140.83333333333329</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>2.0016666666666669</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>56.041666666666657</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <v>48.47</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <f t="shared" si="1"/>
         <v>0.20100277777777786</v>
       </c>
-      <c r="I19" s="2">
+      <c r="J19" s="2">
         <f t="shared" si="2"/>
         <v>4.4520999999999997</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <f t="shared" si="3"/>
         <v>19834.027777777763</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <f t="shared" si="4"/>
         <v>4.0066694444444453</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>3.2063333333333328</v>
       </c>
-      <c r="M19" s="2">
+      <c r="N19" s="2">
         <f t="shared" si="5"/>
         <v>10.280573444444441</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
       <c r="O19">
         <v>0</v>
       </c>
@@ -4032,11 +4177,11 @@
         <v>0</v>
       </c>
       <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
         <v>1</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
         <v>0</v>
       </c>
@@ -4049,55 +4194,58 @@
       <c r="X19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="2">
         <v>0.45500000000000002</v>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
         <v>1.37</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="2">
         <v>124.8333333333333</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="2">
         <v>2.6716666666666669</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <v>64.027777777777771</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <v>53.15</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <f t="shared" si="1"/>
         <v>0.20702500000000001</v>
       </c>
-      <c r="I20" s="2">
+      <c r="J20" s="2">
         <f t="shared" si="2"/>
         <v>1.8769000000000002</v>
       </c>
-      <c r="J20" s="2">
+      <c r="K20" s="2">
         <f t="shared" si="3"/>
         <v>15583.361111111102</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <f t="shared" si="4"/>
         <v>7.1378027777777788</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>4.0881666666666669</v>
       </c>
-      <c r="M20" s="2">
+      <c r="N20" s="2">
         <f t="shared" si="5"/>
         <v>16.713106694444448</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
       <c r="O20">
         <v>0</v>
       </c>
@@ -4111,11 +4259,11 @@
         <v>0</v>
       </c>
       <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
         <v>1</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
         <v>0</v>
       </c>
@@ -4128,55 +4276,58 @@
       <c r="X20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="2">
         <v>0.28999999999999998</v>
       </c>
-      <c r="C21" s="2">
+      <c r="D21" s="2">
         <v>1.208333333333333</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="2">
         <v>131.5333333333333</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="2">
         <v>1.9550000000000001</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>58.819444444444443</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <v>50.08</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <f t="shared" si="1"/>
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="I21" s="2">
+      <c r="J21" s="2">
         <f t="shared" si="2"/>
         <v>1.4600694444444438</v>
       </c>
-      <c r="J21" s="2">
+      <c r="K21" s="2">
         <f t="shared" si="3"/>
         <v>17301.017777777768</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <f t="shared" si="4"/>
         <v>3.8220250000000004</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>3.300333333333334</v>
       </c>
-      <c r="M21" s="2">
+      <c r="N21" s="2">
         <f t="shared" si="5"/>
         <v>10.892200111111116</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
       <c r="O21">
         <v>0</v>
       </c>
@@ -4190,11 +4341,11 @@
         <v>0</v>
       </c>
       <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
         <v>1</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
       <c r="U21">
         <v>0</v>
       </c>
@@ -4207,55 +4358,58 @@
       <c r="X21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="2">
         <v>0.3</v>
       </c>
-      <c r="C22" s="2">
+      <c r="D22" s="2">
         <v>0.97166666666666668</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="2">
         <v>135.15</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="2">
         <v>0.67166666666666663</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>53.055555555555557</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>46.75</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
-      <c r="I22" s="2">
+      <c r="J22" s="2">
         <f t="shared" si="2"/>
         <v>0.94413611111111118</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <f t="shared" si="3"/>
         <v>18265.522500000003</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="2">
         <f t="shared" si="4"/>
         <v>0.45113611111111107</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>2.468</v>
       </c>
-      <c r="M22" s="2">
+      <c r="N22" s="2">
         <f t="shared" si="5"/>
         <v>6.091024</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
       <c r="O22">
         <v>0</v>
       </c>
@@ -4272,11 +4426,11 @@
         <v>0</v>
       </c>
       <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
         <v>1</v>
       </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
       <c r="V22">
         <v>0</v>
       </c>
@@ -4286,55 +4440,58 @@
       <c r="X22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="2">
         <v>1.9233333333333329</v>
       </c>
-      <c r="C23" s="2">
+      <c r="D23" s="2">
         <v>4.2149999999999999</v>
       </c>
-      <c r="D23" s="2">
+      <c r="E23" s="2">
         <v>117.5</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="2">
         <v>1.61</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="2">
         <v>63.75</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23" s="2">
         <v>52.98</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <f t="shared" si="1"/>
         <v>3.6992111111111092</v>
       </c>
-      <c r="I23" s="2">
+      <c r="J23" s="2">
         <f t="shared" si="2"/>
         <v>17.766224999999999</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <f t="shared" si="3"/>
         <v>13806.25</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="2">
         <f t="shared" si="4"/>
         <v>2.5921000000000003</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>7.1173333333333337</v>
       </c>
-      <c r="M23" s="2">
+      <c r="N23" s="2">
         <f t="shared" si="5"/>
         <v>50.656433777777785</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
       <c r="O23">
         <v>0</v>
       </c>
@@ -4351,11 +4508,11 @@
         <v>0</v>
       </c>
       <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
         <v>1</v>
       </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
       <c r="V23">
         <v>0</v>
       </c>
@@ -4365,55 +4522,58 @@
       <c r="X23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="2">
         <v>3.996666666666667</v>
       </c>
-      <c r="C24" s="2">
+      <c r="D24" s="2">
         <v>4.5599999999999996</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="2">
         <v>124.2833333333333</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" s="2">
         <v>1.7033333333333329</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="2">
         <v>68.611111111111114</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="2">
         <v>55.93</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="2">
         <f t="shared" si="1"/>
         <v>15.973344444444447</v>
       </c>
-      <c r="I24" s="2">
+      <c r="J24" s="2">
         <f t="shared" si="2"/>
         <v>20.793599999999998</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <f t="shared" si="3"/>
         <v>15446.346944444436</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <f t="shared" si="4"/>
         <v>2.9013444444444429</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>9.1053333333333342</v>
       </c>
-      <c r="M24" s="2">
+      <c r="N24" s="2">
         <f t="shared" si="5"/>
         <v>82.907095111111133</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
       <c r="O24">
         <v>0</v>
       </c>
@@ -4430,11 +4590,11 @@
         <v>0</v>
       </c>
       <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
         <v>1</v>
       </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
       <c r="V24">
         <v>0</v>
       </c>
@@ -4444,55 +4604,58 @@
       <c r="X24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="2">
         <v>2.041666666666667</v>
       </c>
-      <c r="C25" s="2">
+      <c r="D25" s="2">
         <v>4.5216666666666674</v>
       </c>
-      <c r="D25" s="2">
+      <c r="E25" s="2">
         <v>129.66666666666671</v>
       </c>
-      <c r="E25" s="2">
+      <c r="F25" s="2">
         <v>0.94</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="2">
         <v>68.680555555555557</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25" s="2">
         <v>55.97</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <f t="shared" si="1"/>
         <v>4.1684027777777786</v>
       </c>
-      <c r="I25" s="2">
+      <c r="J25" s="2">
         <f t="shared" si="2"/>
         <v>20.445469444444452</v>
       </c>
-      <c r="J25" s="2">
+      <c r="K25" s="2">
         <f t="shared" si="3"/>
         <v>16813.444444444456</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="2">
         <f t="shared" si="4"/>
         <v>0.88359999999999994</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>7.1029999999999998</v>
       </c>
-      <c r="M25" s="2">
+      <c r="N25" s="2">
         <f t="shared" si="5"/>
         <v>50.452608999999995</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
       <c r="O25">
         <v>0</v>
       </c>
@@ -4509,11 +4672,11 @@
         <v>0</v>
       </c>
       <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
         <v>1</v>
       </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
       <c r="V25">
         <v>0</v>
       </c>
@@ -4523,55 +4686,58 @@
       <c r="X25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="2">
         <v>2.101666666666667</v>
       </c>
-      <c r="C26" s="2">
+      <c r="D26" s="2">
         <v>3.0049999999999999</v>
       </c>
-      <c r="D26" s="2">
+      <c r="E26" s="2">
         <v>126.81666666666671</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F26" s="2">
         <v>1.2716666666666669</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="2">
         <v>50.763888888888893</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26" s="2">
         <v>45.44</v>
       </c>
-      <c r="H26" s="2">
+      <c r="I26" s="2">
         <f t="shared" si="1"/>
         <v>4.4170027777777792</v>
       </c>
-      <c r="I26" s="2">
+      <c r="J26" s="2">
         <f t="shared" si="2"/>
         <v>9.0300250000000002</v>
       </c>
-      <c r="J26" s="2">
+      <c r="K26" s="2">
         <f t="shared" si="3"/>
         <v>16082.466944444453</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="2">
         <f t="shared" si="4"/>
         <v>1.6171361111111118</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>6.1081666666666674</v>
       </c>
-      <c r="M26" s="2">
+      <c r="N26" s="2">
         <f t="shared" si="5"/>
         <v>37.309700027777787</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
       <c r="O26">
         <v>0</v>
       </c>
@@ -4591,66 +4757,69 @@
         <v>0</v>
       </c>
       <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
         <v>1</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
       <c r="W26">
         <v>0</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="2">
         <v>1.1633333333333331</v>
       </c>
-      <c r="C27" s="2">
+      <c r="D27" s="2">
         <v>3.415</v>
       </c>
-      <c r="D27" s="2">
+      <c r="E27" s="2">
         <v>142.51666666666671</v>
       </c>
-      <c r="E27" s="2">
+      <c r="F27" s="2">
         <v>1.96</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="2">
         <v>67.569444444444443</v>
       </c>
-      <c r="G27" s="2">
+      <c r="H27" s="2">
         <v>55.29</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <f t="shared" si="1"/>
         <v>1.353344444444444</v>
       </c>
-      <c r="I27" s="2">
+      <c r="J27" s="2">
         <f t="shared" si="2"/>
         <v>11.662224999999999</v>
       </c>
-      <c r="J27" s="2">
+      <c r="K27" s="2">
         <f t="shared" si="3"/>
         <v>20311.000277777788</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="2">
         <f t="shared" si="4"/>
         <v>3.8415999999999997</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>4.9236666666666666</v>
       </c>
-      <c r="M27" s="2">
+      <c r="N27" s="2">
         <f t="shared" si="5"/>
         <v>24.242493444444445</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
       <c r="O27">
         <v>0</v>
       </c>
@@ -4670,66 +4839,69 @@
         <v>0</v>
       </c>
       <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
         <v>1</v>
       </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
       <c r="W27">
         <v>0</v>
       </c>
       <c r="X27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="2">
         <v>2.933333333333334</v>
       </c>
-      <c r="C28" s="2">
+      <c r="D28" s="2">
         <v>3.5533333333333328</v>
       </c>
-      <c r="D28" s="2">
+      <c r="E28" s="2">
         <v>133.80000000000001</v>
       </c>
-      <c r="E28" s="2">
+      <c r="F28" s="2">
         <v>1.9016666666666671</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="2">
         <v>67.222222222222214</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H28" s="2">
         <v>55.07</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="2">
         <f t="shared" si="1"/>
         <v>8.6044444444444483</v>
       </c>
-      <c r="I28" s="2">
+      <c r="J28" s="2">
         <f t="shared" si="2"/>
         <v>12.626177777777773</v>
       </c>
-      <c r="J28" s="2">
+      <c r="K28" s="2">
         <f t="shared" si="3"/>
         <v>17902.440000000002</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="2">
         <f t="shared" si="4"/>
         <v>3.6163361111111127</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>8.0515000000000008</v>
       </c>
-      <c r="M28" s="2">
+      <c r="N28" s="2">
         <f t="shared" si="5"/>
         <v>64.826652250000009</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
       <c r="O28">
         <v>0</v>
       </c>
@@ -4749,66 +4921,69 @@
         <v>0</v>
       </c>
       <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
         <v>1</v>
       </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
       <c r="W28">
         <v>0</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="2">
         <v>0.59333333333333327</v>
       </c>
-      <c r="C29" s="2">
+      <c r="D29" s="2">
         <v>1.5483333333333329</v>
       </c>
-      <c r="D29" s="2">
+      <c r="E29" s="2">
         <v>113.76666666666669</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" s="2">
         <v>1.95</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="2">
         <v>67.569444444444443</v>
       </c>
-      <c r="G29" s="2">
+      <c r="H29" s="2">
         <v>55.29</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="2">
         <f t="shared" si="1"/>
         <v>0.35204444444444438</v>
       </c>
-      <c r="I29" s="2">
+      <c r="J29" s="2">
         <f t="shared" si="2"/>
         <v>2.3973361111111098</v>
       </c>
-      <c r="J29" s="2">
+      <c r="K29" s="2">
         <f t="shared" si="3"/>
         <v>12942.854444444451</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="2">
         <f t="shared" si="4"/>
         <v>3.8024999999999998</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>4.1866666666666674</v>
       </c>
-      <c r="M29" s="2">
+      <c r="N29" s="2">
         <f t="shared" si="5"/>
         <v>17.528177777777785</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
       <c r="O29">
         <v>0</v>
       </c>
@@ -4828,66 +5003,69 @@
         <v>0</v>
       </c>
       <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
         <v>1</v>
       </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
       <c r="W29">
         <v>0</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="2">
         <v>2.6666666666666668E-2</v>
       </c>
-      <c r="C30" s="2">
+      <c r="D30" s="2">
         <v>0.61833333333333329</v>
       </c>
-      <c r="D30" s="2">
+      <c r="E30" s="2">
         <v>152.1</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="2">
         <v>2.2616666666666672</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="2">
         <v>44.305555555555557</v>
       </c>
-      <c r="G30" s="2">
+      <c r="H30" s="2">
         <v>41.73</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <f t="shared" si="1"/>
         <v>7.1111111111111125E-4</v>
       </c>
-      <c r="I30" s="2">
+      <c r="J30" s="2">
         <f t="shared" si="2"/>
         <v>0.38233611111111104</v>
       </c>
-      <c r="J30" s="2">
+      <c r="K30" s="2">
         <f t="shared" si="3"/>
         <v>23134.41</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="2">
         <f t="shared" si="4"/>
         <v>5.1151361111111138</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>2.121666666666667</v>
       </c>
-      <c r="M30" s="2">
+      <c r="N30" s="2">
         <f t="shared" si="5"/>
         <v>4.5014694444444459</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
       <c r="O30">
         <v>0</v>
       </c>
@@ -4910,63 +5088,66 @@
         <v>0</v>
       </c>
       <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
         <v>1</v>
       </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
       <c r="X30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="2">
         <v>0.90833333333333333</v>
       </c>
-      <c r="C31" s="2">
+      <c r="D31" s="2">
         <v>3.3466666666666671</v>
       </c>
-      <c r="D31" s="2">
+      <c r="E31" s="2">
         <v>122.01666666666669</v>
       </c>
-      <c r="E31" s="2">
+      <c r="F31" s="2">
         <v>0.73666666666666669</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="2">
         <v>58.819444444444443</v>
       </c>
-      <c r="G31" s="2">
+      <c r="H31" s="2">
         <v>50.08</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="2">
         <f t="shared" si="1"/>
         <v>0.82506944444444441</v>
       </c>
-      <c r="I31" s="2">
+      <c r="J31" s="2">
         <f t="shared" si="2"/>
         <v>11.20017777777778</v>
       </c>
-      <c r="J31" s="2">
+      <c r="K31" s="2">
         <f t="shared" si="3"/>
         <v>14888.066944444452</v>
       </c>
-      <c r="K31" s="2">
+      <c r="L31" s="2">
         <f t="shared" si="4"/>
         <v>0.54267777777777781</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>4.7458333333333336</v>
       </c>
-      <c r="M31" s="2">
+      <c r="N31" s="2">
         <f t="shared" si="5"/>
         <v>22.522934027777779</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
       <c r="O31">
         <v>0</v>
       </c>
@@ -4989,63 +5170,66 @@
         <v>0</v>
       </c>
       <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
         <v>1</v>
       </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
       <c r="X31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="2">
         <v>3.57</v>
       </c>
-      <c r="C32" s="2">
+      <c r="D32" s="2">
         <v>4.085</v>
       </c>
-      <c r="D32" s="2">
+      <c r="E32" s="2">
         <v>140.81666666666669</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F32" s="2">
         <v>1.7683333333333331</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="2">
         <v>64.583333333333329</v>
       </c>
-      <c r="G32" s="2">
+      <c r="H32" s="2">
         <v>53.48</v>
       </c>
-      <c r="H32" s="2">
+      <c r="I32" s="2">
         <f t="shared" si="1"/>
         <v>12.744899999999999</v>
       </c>
-      <c r="I32" s="2">
+      <c r="J32" s="2">
         <f t="shared" si="2"/>
         <v>16.687224999999998</v>
       </c>
-      <c r="J32" s="2">
+      <c r="K32" s="2">
         <f t="shared" si="3"/>
         <v>19829.333611111117</v>
       </c>
-      <c r="K32" s="2">
+      <c r="L32" s="2">
         <f t="shared" si="4"/>
         <v>3.1270027777777769</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>6.3025000000000002</v>
       </c>
-      <c r="M32" s="2">
+      <c r="N32" s="2">
         <f t="shared" si="5"/>
         <v>39.721506250000004</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
       <c r="O32">
         <v>0</v>
       </c>
@@ -5068,63 +5252,66 @@
         <v>0</v>
       </c>
       <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
         <v>1</v>
       </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
       <c r="X32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="2">
         <v>0.41333333333333327</v>
       </c>
-      <c r="C33" s="2">
+      <c r="D33" s="2">
         <v>1.29</v>
       </c>
-      <c r="D33" s="2">
+      <c r="E33" s="2">
         <v>126.26666666666669</v>
       </c>
-      <c r="E33" s="2">
+      <c r="F33" s="2">
         <v>2.2349999999999999</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="2">
         <v>64.166666666666671</v>
       </c>
-      <c r="G33" s="2">
+      <c r="H33" s="2">
         <v>53.23</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <f t="shared" si="1"/>
         <v>0.17084444444444441</v>
       </c>
-      <c r="I33" s="2">
+      <c r="J33" s="2">
         <f t="shared" si="2"/>
         <v>1.6641000000000001</v>
       </c>
-      <c r="J33" s="2">
+      <c r="K33" s="2">
         <f t="shared" si="3"/>
         <v>15943.271111111118</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="2">
         <f t="shared" si="4"/>
         <v>4.9952249999999996</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>3.7751666666666668</v>
       </c>
-      <c r="M33" s="2">
+      <c r="N33" s="2">
         <f t="shared" si="5"/>
         <v>14.251883361111112</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
       <c r="O33">
         <v>0</v>
       </c>
@@ -5147,63 +5334,66 @@
         <v>0</v>
       </c>
       <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
         <v>1</v>
       </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
       <c r="X33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="2">
         <v>1.666666666666667E-3</v>
       </c>
-      <c r="C34" s="2">
+      <c r="D34" s="2">
         <v>0.68166666666666664</v>
       </c>
-      <c r="D34" s="2">
+      <c r="E34" s="2">
         <v>137.30000000000001</v>
       </c>
-      <c r="E34" s="2">
+      <c r="F34" s="2">
         <v>1.2133333333333329</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="2">
         <v>48.888888888888893</v>
       </c>
-      <c r="G34" s="2">
+      <c r="H34" s="2">
         <v>44.36</v>
       </c>
-      <c r="H34" s="2">
+      <c r="I34" s="2">
         <f t="shared" si="1"/>
         <v>2.7777777777777788E-6</v>
       </c>
-      <c r="I34" s="2">
+      <c r="J34" s="2">
         <f t="shared" si="2"/>
         <v>0.46466944444444441</v>
       </c>
-      <c r="J34" s="2">
+      <c r="K34" s="2">
         <f t="shared" si="3"/>
         <v>18851.290000000005</v>
       </c>
-      <c r="K34" s="2">
+      <c r="L34" s="2">
         <f t="shared" si="4"/>
         <v>1.4721777777777767</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>2.2925</v>
       </c>
-      <c r="M34" s="2">
+      <c r="N34" s="2">
         <f t="shared" si="5"/>
         <v>5.2555562499999997</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
       <c r="O34">
         <v>0</v>
       </c>
@@ -5229,60 +5419,63 @@
         <v>0</v>
       </c>
       <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
         <v>1</v>
       </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="2">
         <v>1.4750000000000001</v>
       </c>
-      <c r="C35" s="2">
+      <c r="D35" s="2">
         <v>3.5216666666666669</v>
       </c>
-      <c r="D35" s="2">
+      <c r="E35" s="2">
         <v>134.08333333333329</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" s="2">
         <v>2.078333333333334</v>
       </c>
-      <c r="F35" s="2">
+      <c r="G35" s="2">
         <v>63.611111111111107</v>
       </c>
-      <c r="G35" s="2">
+      <c r="H35" s="2">
         <v>52.9</v>
       </c>
-      <c r="H35" s="2">
+      <c r="I35" s="2">
         <f t="shared" si="1"/>
         <v>2.1756250000000001</v>
       </c>
-      <c r="I35" s="2">
+      <c r="J35" s="2">
         <f t="shared" si="2"/>
         <v>12.402136111111114</v>
       </c>
-      <c r="J35" s="2">
+      <c r="K35" s="2">
         <f t="shared" si="3"/>
         <v>17978.340277777766</v>
       </c>
-      <c r="K35" s="2">
+      <c r="L35" s="2">
         <f t="shared" si="4"/>
         <v>4.3194694444444472</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>5.1806666666666663</v>
       </c>
-      <c r="M35" s="2">
+      <c r="N35" s="2">
         <f t="shared" si="5"/>
         <v>26.839307111111108</v>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
       <c r="O35">
         <v>0</v>
       </c>
@@ -5308,60 +5501,63 @@
         <v>0</v>
       </c>
       <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
         <v>1</v>
       </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="2">
         <v>0.64666666666666672</v>
       </c>
-      <c r="C36" s="2">
+      <c r="D36" s="2">
         <v>1.84</v>
       </c>
-      <c r="D36" s="2">
+      <c r="E36" s="2">
         <v>116.8333333333333</v>
       </c>
-      <c r="E36" s="2">
+      <c r="F36" s="2">
         <v>1.8166666666666671</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G36" s="2">
         <v>67.083333333333329</v>
       </c>
-      <c r="G36" s="2">
+      <c r="H36" s="2">
         <v>54.99</v>
       </c>
-      <c r="H36" s="2">
+      <c r="I36" s="2">
         <f t="shared" si="1"/>
         <v>0.41817777777777787</v>
       </c>
-      <c r="I36" s="2">
+      <c r="J36" s="2">
         <f t="shared" si="2"/>
         <v>3.3856000000000002</v>
       </c>
-      <c r="J36" s="2">
+      <c r="K36" s="2">
         <f t="shared" si="3"/>
         <v>13650.02777777777</v>
       </c>
-      <c r="K36" s="2">
+      <c r="L36" s="2">
         <f t="shared" si="4"/>
         <v>3.3002777777777794</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>4.5996666666666668</v>
       </c>
-      <c r="M36" s="2">
+      <c r="N36" s="2">
         <f t="shared" si="5"/>
         <v>21.156933444444444</v>
       </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
       <c r="O36">
         <v>0</v>
       </c>
@@ -5387,60 +5583,63 @@
         <v>0</v>
       </c>
       <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
         <v>1</v>
       </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="2">
         <v>0.45</v>
       </c>
-      <c r="C37" s="2">
+      <c r="D37" s="2">
         <v>1.3866666666666669</v>
       </c>
-      <c r="D37" s="2">
+      <c r="E37" s="2">
         <v>125.4166666666667</v>
       </c>
-      <c r="E37" s="2">
+      <c r="F37" s="2">
         <v>1.845</v>
       </c>
-      <c r="F37" s="2">
+      <c r="G37" s="2">
         <v>66.180555555555557</v>
       </c>
-      <c r="G37" s="2">
+      <c r="H37" s="2">
         <v>54.44</v>
       </c>
-      <c r="H37" s="2">
+      <c r="I37" s="2">
         <f t="shared" si="1"/>
         <v>0.20250000000000001</v>
       </c>
-      <c r="I37" s="2">
+      <c r="J37" s="2">
         <f t="shared" si="2"/>
         <v>1.9228444444444452</v>
       </c>
-      <c r="J37" s="2">
+      <c r="K37" s="2">
         <f t="shared" si="3"/>
         <v>15729.340277777786</v>
       </c>
-      <c r="K37" s="2">
+      <c r="L37" s="2">
         <f t="shared" si="4"/>
         <v>3.4040249999999999</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>4.418333333333333</v>
       </c>
-      <c r="M37" s="2">
+      <c r="N37" s="2">
         <f t="shared" si="5"/>
         <v>19.521669444444441</v>
       </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
       <c r="O37">
         <v>0</v>
       </c>
@@ -5466,60 +5665,63 @@
         <v>0</v>
       </c>
       <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
         <v>1</v>
       </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="2">
         <v>0.1183333333333333</v>
       </c>
-      <c r="C38" s="2">
+      <c r="D38" s="2">
         <v>0.53666666666666663</v>
       </c>
-      <c r="D38" s="2">
+      <c r="E38" s="2">
         <v>182.15</v>
       </c>
-      <c r="E38" s="2">
-        <v>0</v>
-      </c>
       <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
         <v>35.902777777777779</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>36.81</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <f t="shared" si="1"/>
         <v>1.400277777777777E-2</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <f t="shared" si="2"/>
         <v>0.28801111111111105</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <f t="shared" si="3"/>
         <v>33178.622500000005</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>2.4148333333333332</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <f t="shared" si="5"/>
         <v>5.831420027777777</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
       <c r="O38">
         <v>0</v>
       </c>
@@ -5548,57 +5750,60 @@
         <v>0</v>
       </c>
       <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="2">
         <v>1.1166666666666669</v>
       </c>
-      <c r="C39" s="2">
+      <c r="D39" s="2">
         <v>3.3583333333333329</v>
       </c>
-      <c r="D39" s="2">
+      <c r="E39" s="2">
         <v>135.3833333333333</v>
       </c>
-      <c r="E39" s="2">
+      <c r="F39" s="2">
         <v>1.5549999999999999</v>
       </c>
-      <c r="F39" s="2">
+      <c r="G39" s="2">
         <v>48.194444444444443</v>
       </c>
-      <c r="G39" s="2">
+      <c r="H39" s="2">
         <v>43.97</v>
       </c>
-      <c r="H39" s="2">
+      <c r="I39" s="2">
         <f t="shared" si="1"/>
         <v>1.2469444444444451</v>
       </c>
-      <c r="I39" s="2">
+      <c r="J39" s="2">
         <f t="shared" si="2"/>
         <v>11.278402777777774</v>
       </c>
-      <c r="J39" s="2">
+      <c r="K39" s="2">
         <f t="shared" si="3"/>
         <v>18328.646944444434</v>
       </c>
-      <c r="K39" s="2">
+      <c r="L39" s="2">
         <f t="shared" si="4"/>
         <v>2.4180249999999996</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>5.2380000000000004</v>
       </c>
-      <c r="M39" s="2">
+      <c r="N39" s="2">
         <f t="shared" si="5"/>
         <v>27.436644000000005</v>
       </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
       <c r="O39">
         <v>0</v>
       </c>
@@ -5627,57 +5832,60 @@
         <v>0</v>
       </c>
       <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="2">
         <v>2.3266666666666671</v>
       </c>
-      <c r="C40" s="2">
+      <c r="D40" s="2">
         <v>3.5016666666666669</v>
       </c>
-      <c r="D40" s="2">
+      <c r="E40" s="2">
         <v>114.68333333333329</v>
       </c>
-      <c r="E40" s="2">
+      <c r="F40" s="2">
         <v>1.52</v>
       </c>
-      <c r="F40" s="2">
+      <c r="G40" s="2">
         <v>64.097222222222229</v>
       </c>
-      <c r="G40" s="2">
+      <c r="H40" s="2">
         <v>53.19</v>
       </c>
-      <c r="H40" s="2">
+      <c r="I40" s="2">
         <f t="shared" si="1"/>
         <v>5.4133777777777796</v>
       </c>
-      <c r="I40" s="2">
+      <c r="J40" s="2">
         <f t="shared" si="2"/>
         <v>12.261669444444447</v>
       </c>
-      <c r="J40" s="2">
+      <c r="K40" s="2">
         <f t="shared" si="3"/>
         <v>13152.266944444436</v>
       </c>
-      <c r="K40" s="2">
+      <c r="L40" s="2">
         <f t="shared" si="4"/>
         <v>2.3104</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>7.6448333333333336</v>
       </c>
-      <c r="M40" s="2">
+      <c r="N40" s="2">
         <f t="shared" si="5"/>
         <v>58.443476694444449</v>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
       <c r="O40">
         <v>0</v>
       </c>
@@ -5706,57 +5914,60 @@
         <v>0</v>
       </c>
       <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="2">
         <v>1.958333333333333</v>
       </c>
-      <c r="C41" s="2">
+      <c r="D41" s="2">
         <v>4.2216666666666667</v>
       </c>
-      <c r="D41" s="2">
+      <c r="E41" s="2">
         <v>132.23333333333329</v>
       </c>
-      <c r="E41" s="2">
+      <c r="F41" s="2">
         <v>1.4116666666666671</v>
       </c>
-      <c r="F41" s="2">
+      <c r="G41" s="2">
         <v>65.972222222222229</v>
       </c>
-      <c r="G41" s="2">
+      <c r="H41" s="2">
         <v>54.31</v>
       </c>
-      <c r="H41" s="2">
+      <c r="I41" s="2">
         <f t="shared" si="1"/>
         <v>3.8350694444444433</v>
       </c>
-      <c r="I41" s="2">
+      <c r="J41" s="2">
         <f t="shared" si="2"/>
         <v>17.822469444444444</v>
       </c>
-      <c r="J41" s="2">
+      <c r="K41" s="2">
         <f t="shared" si="3"/>
         <v>17485.654444444433</v>
       </c>
-      <c r="K41" s="2">
+      <c r="L41" s="2">
         <f t="shared" si="4"/>
         <v>1.9928027777777788</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>6.6663333333333332</v>
       </c>
-      <c r="M41" s="2">
+      <c r="N41" s="2">
         <f t="shared" si="5"/>
         <v>44.440000111111111</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
       <c r="O41">
         <v>0</v>
       </c>
@@ -5785,6 +5996,9 @@
         <v>0</v>
       </c>
       <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
         <v>1</v>
       </c>
     </row>

--- a/Df_medie_chem.xlsx
+++ b/Df_medie_chem.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorenzo.chiapparoli\Documents\Dataset_completo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utente\Documents\Dataset_completo\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F3F148-4DDB-484C-9806-B1874DCA9BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chem_media" sheetId="1" r:id="rId1"/>
     <sheet name="fit" sheetId="2" r:id="rId2"/>
     <sheet name="Foglio2" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="95">
   <si>
     <t>Micro</t>
   </si>
@@ -324,7 +326,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -433,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -449,7 +451,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -469,14 +471,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -514,9 +512,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -551,7 +549,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -586,7 +584,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -759,34 +757,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" customWidth="1"/>
-    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" customWidth="1"/>
+    <col min="18" max="18" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +873,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -941,7 +939,7 @@
       </c>
       <c r="V2" s="2"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1051,7 +1049,7 @@
         <v>12.572125622246535</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1161,7 +1159,7 @@
         <v>7.6956646244454401</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1271,7 +1269,7 @@
         <v>18.61953566369419</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1306,7 +1304,7 @@
         <v>36.597222222222221</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
@@ -1341,7 +1339,7 @@
         <v>39.583333333333343</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1376,7 +1374,7 @@
         <v>40.972222222222221</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
@@ -1411,7 +1409,7 @@
         <v>42.361111111111107</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -1446,7 +1444,7 @@
         <v>44.097222222222221</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
@@ -1481,7 +1479,7 @@
         <v>44.305555555555557</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
@@ -1516,7 +1514,7 @@
         <v>48.194444444444443</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -1551,7 +1549,7 @@
         <v>48.888888888888893</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>4</v>
       </c>
@@ -1586,7 +1584,7 @@
         <v>49.791666666666671</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>25</v>
       </c>
@@ -1621,7 +1619,7 @@
         <v>50.763888888888893</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>13</v>
       </c>
@@ -1656,7 +1654,7 @@
         <v>50.972222222222221</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
@@ -1691,7 +1689,7 @@
         <v>51.597222222222221</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1726,7 +1724,7 @@
         <v>53.055555555555557</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>5</v>
       </c>
@@ -1761,7 +1759,7 @@
         <v>54.513888888888893</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>18</v>
       </c>
@@ -1796,7 +1794,7 @@
         <v>56.041666666666657</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
@@ -1831,7 +1829,7 @@
         <v>58.819444444444443</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
@@ -1866,7 +1864,7 @@
         <v>58.819444444444443</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>14</v>
       </c>
@@ -1901,7 +1899,7 @@
         <v>58.958333333333343</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>8</v>
       </c>
@@ -1936,7 +1934,7 @@
         <v>59.583333333333343</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>9</v>
       </c>
@@ -1971,7 +1969,7 @@
         <v>63.263888888888893</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2006,7 +2004,7 @@
         <v>63.611111111111107</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>22</v>
       </c>
@@ -2041,7 +2039,7 @@
         <v>63.75</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>19</v>
       </c>
@@ -2076,7 +2074,7 @@
         <v>64.027777777777771</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
@@ -2111,7 +2109,7 @@
         <v>64.097222222222229</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>32</v>
       </c>
@@ -2146,7 +2144,7 @@
         <v>64.166666666666671</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -2181,7 +2179,7 @@
         <v>64.583333333333329</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
@@ -2216,7 +2214,7 @@
         <v>65.972222222222229</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>36</v>
       </c>
@@ -2251,7 +2249,7 @@
         <v>66.180555555555557</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>35</v>
       </c>
@@ -2286,7 +2284,7 @@
         <v>67.083333333333329</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>27</v>
       </c>
@@ -2321,7 +2319,7 @@
         <v>67.222222222222214</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>10</v>
       </c>
@@ -2356,7 +2354,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>26</v>
       </c>
@@ -2391,7 +2389,7 @@
         <v>67.569444444444443</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>28</v>
       </c>
@@ -2426,7 +2424,7 @@
         <v>67.569444444444443</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>23</v>
       </c>
@@ -2461,7 +2459,7 @@
         <v>68.611111111111114</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>24</v>
       </c>
@@ -2496,7 +2494,7 @@
         <v>68.680555555555557</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>11</v>
       </c>
@@ -2532,7 +2530,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:K43">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K43">
     <sortCondition ref="K1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2540,21 +2538,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2628,7 +2626,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2707,7 +2705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2786,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2865,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2911,7 +2909,7 @@
         <v>31.802832360000004</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -2944,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2993,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -3023,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3069,10 +3067,10 @@
         <v>43.55780002777778</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -3102,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3181,7 +3179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3260,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3339,7 +3337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3385,7 +3383,7 @@
         <v>58.438380249999994</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3418,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3467,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3497,7 +3495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -3543,10 +3541,10 @@
         <v>68.804260027777772</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3576,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3655,7 +3653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3701,7 +3699,7 @@
         <v>44.504464694444451</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3734,7 +3732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3783,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3813,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -3859,10 +3857,10 @@
         <v>26.582617361111105</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3892,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -3971,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -4017,7 +4015,7 @@
         <v>10.280573444444441</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4050,7 +4048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -4099,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4129,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -4175,10 +4173,10 @@
         <v>10.892200111111116</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4208,7 +4206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -4287,7 +4285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -4333,7 +4331,7 @@
         <v>50.656433777777785</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4366,7 +4364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -4415,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -4445,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -4491,10 +4489,10 @@
         <v>50.452608999999995</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -4524,7 +4522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -4603,7 +4601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4649,7 +4647,7 @@
         <v>24.242493444444445</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4682,7 +4680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -4731,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -4761,7 +4759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -4807,10 +4805,10 @@
         <v>17.528177777777785</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -4840,7 +4838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -4919,7 +4917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -4965,7 +4963,7 @@
         <v>22.522934027777779</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4998,7 +4996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -5047,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -5077,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -5123,10 +5121,10 @@
         <v>14.251883361111112</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -5156,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -5235,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -5281,7 +5279,7 @@
         <v>26.839307111111108</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5314,7 +5312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -5363,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -5393,7 +5391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -5439,10 +5437,10 @@
         <v>19.521669444444441</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -5472,7 +5470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -5551,7 +5549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -5597,7 +5595,7 @@
         <v>27.436644000000005</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5630,7 +5628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -5679,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -5709,7 +5707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -5755,10 +5753,10 @@
         <v>44.440000111111111</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -5789,7 +5787,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A3:K41">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K41">
     <sortCondition ref="A3"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5798,15 +5796,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5877,7 +5875,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>84</v>
       </c>
@@ -5954,7 +5952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -6031,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -6108,7 +6106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -6185,7 +6183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -6262,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6339,7 +6337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6416,7 +6414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -6493,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>86</v>
       </c>
@@ -6570,7 +6568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>13</v>
       </c>
@@ -6647,7 +6645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>14</v>
       </c>
@@ -6724,7 +6722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>15</v>
       </c>
@@ -6801,7 +6799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -6878,7 +6876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6955,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -7032,7 +7030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -7109,7 +7107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>88</v>
       </c>
@@ -7186,7 +7184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>22</v>
       </c>
@@ -7263,7 +7261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>23</v>
       </c>
@@ -7340,7 +7338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>24</v>
       </c>
@@ -7417,7 +7415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>89</v>
       </c>
@@ -7494,7 +7492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -7571,7 +7569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -7648,7 +7646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -7725,7 +7723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>90</v>
       </c>
@@ -7802,7 +7800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>30</v>
       </c>
@@ -7879,7 +7877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>31</v>
       </c>
@@ -7956,7 +7954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>32</v>
       </c>
@@ -8033,7 +8031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -8110,7 +8108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -8187,7 +8185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -8264,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -8341,7 +8339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>92</v>
       </c>
@@ -8418,7 +8416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>38</v>
       </c>
@@ -8495,7 +8493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>39</v>
       </c>
@@ -8572,7 +8570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>40</v>
       </c>
@@ -8646,6 +8644,3023 @@
         <v>0</v>
       </c>
       <c r="W37" s="9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE60B6E7-1549-42BF-9BAA-082B8883328D}">
+  <dimension ref="A1:X38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" t="s">
+        <v>68</v>
+      </c>
+      <c r="S1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1.666666666666667E-3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.37666666666666659</v>
+      </c>
+      <c r="D2" s="2">
+        <v>221.4</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <f>B2^2</f>
+        <v>2.7777777777777788E-6</v>
+      </c>
+      <c r="I2" s="2">
+        <f t="shared" ref="I2:K14" si="0">C2^2</f>
+        <v>0.14187777777777771</v>
+      </c>
+      <c r="J2" s="2">
+        <f t="shared" si="0"/>
+        <v>49017.96</v>
+      </c>
+      <c r="K2" s="2">
+        <f t="shared" si="0"/>
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="L2">
+        <v>2.004666666666667</v>
+      </c>
+      <c r="M2" s="2">
+        <f>L2^2</f>
+        <v>4.0186884444444457</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3.333333333333334E-3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.26833333333333331</v>
+      </c>
+      <c r="D3" s="2">
+        <v>199.15</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.34666666666666668</v>
+      </c>
+      <c r="F3" s="2">
+        <v>16.18055555555555</v>
+      </c>
+      <c r="G3" s="2">
+        <v>23.72</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:K38" si="1">B3^2</f>
+        <v>1.1111111111111115E-5</v>
+      </c>
+      <c r="I3" s="2">
+        <f t="shared" si="0"/>
+        <v>7.2002777777777763E-2</v>
+      </c>
+      <c r="J3" s="2">
+        <f t="shared" si="0"/>
+        <v>39660.722500000003</v>
+      </c>
+      <c r="K3" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12017777777777779</v>
+      </c>
+      <c r="L3">
+        <v>2.3210000000000002</v>
+      </c>
+      <c r="M3" s="2">
+        <f t="shared" ref="M3:M38" si="2">L3^2</f>
+        <v>5.3870410000000009</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2.6983333333333328</v>
+      </c>
+      <c r="D4" s="2">
+        <v>155.23333333333329</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.5149999999999999</v>
+      </c>
+      <c r="F4" s="2">
+        <v>44.097222222222221</v>
+      </c>
+      <c r="G4" s="2">
+        <v>41.61</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0404</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" si="0"/>
+        <v>7.2810027777777746</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" si="0"/>
+        <v>24097.387777777763</v>
+      </c>
+      <c r="K4" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2952249999999998</v>
+      </c>
+      <c r="L4">
+        <v>5.6394000000000002</v>
+      </c>
+      <c r="M4" s="2">
+        <f t="shared" si="2"/>
+        <v>31.802832360000004</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1.865</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3.4833333333333329</v>
+      </c>
+      <c r="D5" s="2">
+        <v>134.4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.89</v>
+      </c>
+      <c r="F5" s="2">
+        <v>49.791666666666671</v>
+      </c>
+      <c r="G5" s="2">
+        <v>44.88</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>3.4782250000000001</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="0"/>
+        <v>12.133611111111108</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="0"/>
+        <v>18063.36</v>
+      </c>
+      <c r="K5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79210000000000003</v>
+      </c>
+      <c r="L5">
+        <v>6.6719999999999997</v>
+      </c>
+      <c r="M5" s="2">
+        <f t="shared" si="2"/>
+        <v>44.515583999999997</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2.5733333333333328</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4.2350000000000003</v>
+      </c>
+      <c r="D6" s="2">
+        <v>147.56666666666669</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F6" s="2">
+        <v>54.513888888888893</v>
+      </c>
+      <c r="G6" s="2">
+        <v>47.59</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>6.622044444444442</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="0"/>
+        <v>17.935225000000003</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" si="0"/>
+        <v>21775.921111111118</v>
+      </c>
+      <c r="K6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L6">
+        <v>6.5998333333333337</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" si="2"/>
+        <v>43.55780002777778</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1.3666666666666669</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.9716666666666669</v>
+      </c>
+      <c r="D7" s="2">
+        <v>147.55000000000001</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.658333333333333</v>
+      </c>
+      <c r="F7" s="2">
+        <v>59.583333333333343</v>
+      </c>
+      <c r="G7" s="2">
+        <v>50.53</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8677777777777784</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="0"/>
+        <v>3.8874694444444455</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" si="0"/>
+        <v>21771.002500000002</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7500694444444433</v>
+      </c>
+      <c r="L7">
+        <v>4.2358333333333338</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="2"/>
+        <v>17.942284027777781</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2.7866666666666671</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4.7450000000000001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>123.43333333333329</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.405</v>
+      </c>
+      <c r="F8" s="2">
+        <v>63.263888888888893</v>
+      </c>
+      <c r="G8" s="2">
+        <v>52.69</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>7.7655111111111133</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="0"/>
+        <v>22.515025000000001</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" si="0"/>
+        <v>15235.787777777768</v>
+      </c>
+      <c r="K8" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9740250000000001</v>
+      </c>
+      <c r="L8">
+        <v>7.6444999999999999</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="2"/>
+        <v>58.438380249999994</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>4.3083333333333336</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4.7616666666666667</v>
+      </c>
+      <c r="D9" s="2">
+        <v>114.48333333333331</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1.5866666666666669</v>
+      </c>
+      <c r="F9" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="G9" s="2">
+        <v>55.24</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>18.561736111111113</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="0"/>
+        <v>22.673469444444446</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" si="0"/>
+        <v>13106.433611111104</v>
+      </c>
+      <c r="K9" s="2">
+        <f t="shared" si="0"/>
+        <v>2.5175111111111117</v>
+      </c>
+      <c r="L9">
+        <v>9.0151666666666657</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="2"/>
+        <v>81.273230027777757</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3.121666666666667</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5.0983333333333336</v>
+      </c>
+      <c r="D10" s="2">
+        <v>126.05</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.89166666666666661</v>
+      </c>
+      <c r="F10" s="2">
+        <v>68.75</v>
+      </c>
+      <c r="G10" s="2">
+        <v>56.01</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>9.7448027777777799</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="0"/>
+        <v>25.993002777777779</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="0"/>
+        <v>15888.602499999999</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79506944444444438</v>
+      </c>
+      <c r="L10">
+        <v>8.2948333333333331</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="2"/>
+        <v>68.804260027777772</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1.666666666666667E-3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.2466666666666667</v>
+      </c>
+      <c r="D11" s="2">
+        <v>185.2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.69333333333333336</v>
+      </c>
+      <c r="F11" s="2">
+        <v>18.611111111111111</v>
+      </c>
+      <c r="G11" s="2">
+        <v>25.56</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7777777777777788E-6</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="0"/>
+        <v>6.0844444444444458E-2</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="0"/>
+        <v>34299.039999999994</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.48071111111111114</v>
+      </c>
+      <c r="L11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="2"/>
+        <v>4.8400000000000007</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2.105</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4.0949999999999998</v>
+      </c>
+      <c r="D12" s="2">
+        <v>137.0333333333333</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.1233333333333331</v>
+      </c>
+      <c r="F12" s="2">
+        <v>50.972222222222221</v>
+      </c>
+      <c r="G12" s="2">
+        <v>45.56</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>4.431025</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="0"/>
+        <v>16.769024999999999</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="0"/>
+        <v>18778.134444444437</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.2618777777777772</v>
+      </c>
+      <c r="L12">
+        <v>6.6711666666666671</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="2"/>
+        <v>44.504464694444451</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1.8566666666666669</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3.8666666666666671</v>
+      </c>
+      <c r="D13" s="2">
+        <v>132</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.48</v>
+      </c>
+      <c r="F13" s="2">
+        <v>58.958333333333343</v>
+      </c>
+      <c r="G13" s="2">
+        <v>50.16</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>3.4472111111111121</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="0"/>
+        <v>14.951111111111114</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" si="0"/>
+        <v>17424</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="0"/>
+        <v>2.1903999999999999</v>
+      </c>
+      <c r="L13">
+        <v>6.1544999999999996</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="2"/>
+        <v>37.877870249999994</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1.611666666666667</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4.1383333333333336</v>
+      </c>
+      <c r="D14" s="2">
+        <v>164.16666666666671</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.44166666666666671</v>
+      </c>
+      <c r="F14" s="2">
+        <v>51.597222222222221</v>
+      </c>
+      <c r="G14" s="2">
+        <v>45.92</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5974694444444455</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="0"/>
+        <v>17.125802777777782</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="0"/>
+        <v>26950.69444444446</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.19506944444444449</v>
+      </c>
+      <c r="L14">
+        <v>5.1558333333333328</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="2"/>
+        <v>26.582617361111105</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.64166666666666661</v>
+      </c>
+      <c r="D15" s="2">
+        <v>160.66666666666671</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.1516666666666667</v>
+      </c>
+      <c r="F15" s="2">
+        <v>42.361111111111107</v>
+      </c>
+      <c r="G15" s="2">
+        <v>40.61</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>1E-4</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="1"/>
+        <v>0.41173611111111103</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="1"/>
+        <v>25813.777777777792</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3002777777777789E-2</v>
+      </c>
+      <c r="L15">
+        <v>2.036</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="2"/>
+        <v>4.1452960000000001</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.44833333333333342</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.11</v>
+      </c>
+      <c r="D16" s="2">
+        <v>140.83333333333329</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.0016666666666669</v>
+      </c>
+      <c r="F16" s="2">
+        <v>56.041666666666657</v>
+      </c>
+      <c r="G16" s="2">
+        <v>48.47</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.20100277777777786</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="1"/>
+        <v>4.4520999999999997</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="1"/>
+        <v>19834.027777777763</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="1"/>
+        <v>4.0066694444444453</v>
+      </c>
+      <c r="L16">
+        <v>3.2063333333333328</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="2"/>
+        <v>10.280573444444441</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1.37</v>
+      </c>
+      <c r="D17" s="2">
+        <v>124.8333333333333</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2.6716666666666669</v>
+      </c>
+      <c r="F17" s="2">
+        <v>64.027777777777771</v>
+      </c>
+      <c r="G17" s="2">
+        <v>53.15</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>0.20702500000000001</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8769000000000002</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" si="1"/>
+        <v>15583.361111111102</v>
+      </c>
+      <c r="K17" s="2">
+        <f t="shared" si="1"/>
+        <v>7.1378027777777788</v>
+      </c>
+      <c r="L17">
+        <v>4.0881666666666669</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="2"/>
+        <v>16.713106694444448</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="D18" s="2">
+        <v>131.5333333333333</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.9550000000000001</v>
+      </c>
+      <c r="F18" s="2">
+        <v>58.819444444444443</v>
+      </c>
+      <c r="G18" s="2">
+        <v>50.08</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>8.4099999999999994E-2</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4600694444444438</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="1"/>
+        <v>17301.017777777768</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="1"/>
+        <v>3.8220250000000004</v>
+      </c>
+      <c r="L18">
+        <v>3.300333333333334</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="2"/>
+        <v>10.892200111111116</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.97166666666666668</v>
+      </c>
+      <c r="D19" s="2">
+        <v>135.15</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.67166666666666663</v>
+      </c>
+      <c r="F19" s="2">
+        <v>53.055555555555557</v>
+      </c>
+      <c r="G19" s="2">
+        <v>46.75</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>0.09</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="1"/>
+        <v>0.94413611111111118</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" si="1"/>
+        <v>18265.522500000003</v>
+      </c>
+      <c r="K19" s="2">
+        <f t="shared" si="1"/>
+        <v>0.45113611111111107</v>
+      </c>
+      <c r="L19">
+        <v>2.468</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="2"/>
+        <v>6.091024</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.9233333333333329</v>
+      </c>
+      <c r="C20" s="2">
+        <v>4.2149999999999999</v>
+      </c>
+      <c r="D20" s="2">
+        <v>117.5</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.61</v>
+      </c>
+      <c r="F20" s="2">
+        <v>63.75</v>
+      </c>
+      <c r="G20" s="2">
+        <v>52.98</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="1"/>
+        <v>3.6992111111111092</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="1"/>
+        <v>17.766224999999999</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" si="1"/>
+        <v>13806.25</v>
+      </c>
+      <c r="K20" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5921000000000003</v>
+      </c>
+      <c r="L20">
+        <v>7.1173333333333337</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="2"/>
+        <v>50.656433777777785</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3.996666666666667</v>
+      </c>
+      <c r="C21" s="2">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="D21" s="2">
+        <v>124.2833333333333</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.7033333333333329</v>
+      </c>
+      <c r="F21" s="2">
+        <v>68.611111111111114</v>
+      </c>
+      <c r="G21" s="2">
+        <v>55.93</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>15.973344444444447</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="1"/>
+        <v>20.793599999999998</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" si="1"/>
+        <v>15446.346944444436</v>
+      </c>
+      <c r="K21" s="2">
+        <f t="shared" si="1"/>
+        <v>2.9013444444444429</v>
+      </c>
+      <c r="L21">
+        <v>9.1053333333333342</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="2"/>
+        <v>82.907095111111133</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2.041666666666667</v>
+      </c>
+      <c r="C22" s="2">
+        <v>4.5216666666666674</v>
+      </c>
+      <c r="D22" s="2">
+        <v>129.66666666666671</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F22" s="2">
+        <v>68.680555555555557</v>
+      </c>
+      <c r="G22" s="2">
+        <v>55.97</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="1"/>
+        <v>4.1684027777777786</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="1"/>
+        <v>20.445469444444452</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" si="1"/>
+        <v>16813.444444444456</v>
+      </c>
+      <c r="K22" s="2">
+        <f t="shared" si="1"/>
+        <v>0.88359999999999994</v>
+      </c>
+      <c r="L22">
+        <v>7.1029999999999998</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="2"/>
+        <v>50.452608999999995</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2.101666666666667</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="D23" s="2">
+        <v>126.81666666666671</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1.2716666666666669</v>
+      </c>
+      <c r="F23" s="2">
+        <v>50.763888888888893</v>
+      </c>
+      <c r="G23" s="2">
+        <v>45.44</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="1"/>
+        <v>4.4170027777777792</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="1"/>
+        <v>9.0300250000000002</v>
+      </c>
+      <c r="J23" s="2">
+        <f t="shared" si="1"/>
+        <v>16082.466944444453</v>
+      </c>
+      <c r="K23" s="2">
+        <f t="shared" si="1"/>
+        <v>1.6171361111111118</v>
+      </c>
+      <c r="L23">
+        <v>6.1081666666666674</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="2"/>
+        <v>37.309700027777787</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1.1633333333333331</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3.415</v>
+      </c>
+      <c r="D24" s="2">
+        <v>142.51666666666671</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.96</v>
+      </c>
+      <c r="F24" s="2">
+        <v>67.569444444444443</v>
+      </c>
+      <c r="G24" s="2">
+        <v>55.29</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="1"/>
+        <v>1.353344444444444</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="1"/>
+        <v>11.662224999999999</v>
+      </c>
+      <c r="J24" s="2">
+        <f t="shared" si="1"/>
+        <v>20311.000277777788</v>
+      </c>
+      <c r="K24" s="2">
+        <f t="shared" si="1"/>
+        <v>3.8415999999999997</v>
+      </c>
+      <c r="L24">
+        <v>4.9236666666666666</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="2"/>
+        <v>24.242493444444445</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2.933333333333334</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3.5533333333333328</v>
+      </c>
+      <c r="D25" s="2">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1.9016666666666671</v>
+      </c>
+      <c r="F25" s="2">
+        <v>67.222222222222214</v>
+      </c>
+      <c r="G25" s="2">
+        <v>55.07</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" si="1"/>
+        <v>8.6044444444444483</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" si="1"/>
+        <v>12.626177777777773</v>
+      </c>
+      <c r="J25" s="2">
+        <f t="shared" si="1"/>
+        <v>17902.440000000002</v>
+      </c>
+      <c r="K25" s="2">
+        <f t="shared" si="1"/>
+        <v>3.6163361111111127</v>
+      </c>
+      <c r="L25">
+        <v>8.0515000000000008</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" si="2"/>
+        <v>64.826652250000009</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.59333333333333327</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1.5483333333333329</v>
+      </c>
+      <c r="D26" s="2">
+        <v>113.76666666666669</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1.95</v>
+      </c>
+      <c r="F26" s="2">
+        <v>67.569444444444443</v>
+      </c>
+      <c r="G26" s="2">
+        <v>55.29</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="1"/>
+        <v>0.35204444444444438</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3973361111111098</v>
+      </c>
+      <c r="J26" s="2">
+        <f t="shared" si="1"/>
+        <v>12942.854444444451</v>
+      </c>
+      <c r="K26" s="2">
+        <f t="shared" si="1"/>
+        <v>3.8024999999999998</v>
+      </c>
+      <c r="L26">
+        <v>4.1866666666666674</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="2"/>
+        <v>17.528177777777785</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2.6666666666666668E-2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.61833333333333329</v>
+      </c>
+      <c r="D27" s="2">
+        <v>152.1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2.2616666666666672</v>
+      </c>
+      <c r="F27" s="2">
+        <v>44.305555555555557</v>
+      </c>
+      <c r="G27" s="2">
+        <v>41.73</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="1"/>
+        <v>7.1111111111111125E-4</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="1"/>
+        <v>0.38233611111111104</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" si="1"/>
+        <v>23134.41</v>
+      </c>
+      <c r="K27" s="2">
+        <f t="shared" si="1"/>
+        <v>5.1151361111111138</v>
+      </c>
+      <c r="L27">
+        <v>2.121666666666667</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="2"/>
+        <v>4.5014694444444459</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3.3466666666666671</v>
+      </c>
+      <c r="D28" s="2">
+        <v>122.01666666666669</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.73666666666666669</v>
+      </c>
+      <c r="F28" s="2">
+        <v>58.819444444444443</v>
+      </c>
+      <c r="G28" s="2">
+        <v>50.08</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="1"/>
+        <v>0.82506944444444441</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="1"/>
+        <v>11.20017777777778</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" si="1"/>
+        <v>14888.066944444452</v>
+      </c>
+      <c r="K28" s="2">
+        <f t="shared" si="1"/>
+        <v>0.54267777777777781</v>
+      </c>
+      <c r="L28">
+        <v>4.7458333333333336</v>
+      </c>
+      <c r="M28" s="2">
+        <f t="shared" si="2"/>
+        <v>22.522934027777779</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2">
+        <v>3.57</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4.085</v>
+      </c>
+      <c r="D29" s="2">
+        <v>140.81666666666669</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1.7683333333333331</v>
+      </c>
+      <c r="F29" s="2">
+        <v>64.583333333333329</v>
+      </c>
+      <c r="G29" s="2">
+        <v>53.48</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="1"/>
+        <v>12.744899999999999</v>
+      </c>
+      <c r="I29" s="2">
+        <f t="shared" si="1"/>
+        <v>16.687224999999998</v>
+      </c>
+      <c r="J29" s="2">
+        <f t="shared" si="1"/>
+        <v>19829.333611111117</v>
+      </c>
+      <c r="K29" s="2">
+        <f t="shared" si="1"/>
+        <v>3.1270027777777769</v>
+      </c>
+      <c r="L29">
+        <v>6.3025000000000002</v>
+      </c>
+      <c r="M29" s="2">
+        <f t="shared" si="2"/>
+        <v>39.721506250000004</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.41333333333333327</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1.29</v>
+      </c>
+      <c r="D30" s="2">
+        <v>126.26666666666669</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2.2349999999999999</v>
+      </c>
+      <c r="F30" s="2">
+        <v>64.166666666666671</v>
+      </c>
+      <c r="G30" s="2">
+        <v>53.23</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="1"/>
+        <v>0.17084444444444441</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="1"/>
+        <v>1.6641000000000001</v>
+      </c>
+      <c r="J30" s="2">
+        <f t="shared" si="1"/>
+        <v>15943.271111111118</v>
+      </c>
+      <c r="K30" s="2">
+        <f t="shared" si="1"/>
+        <v>4.9952249999999996</v>
+      </c>
+      <c r="L30">
+        <v>3.7751666666666668</v>
+      </c>
+      <c r="M30" s="2">
+        <f t="shared" si="2"/>
+        <v>14.251883361111112</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="2">
+        <v>1.666666666666667E-3</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.68166666666666664</v>
+      </c>
+      <c r="D31" s="2">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1.2133333333333329</v>
+      </c>
+      <c r="F31" s="2">
+        <v>48.888888888888893</v>
+      </c>
+      <c r="G31" s="2">
+        <v>44.36</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7777777777777788E-6</v>
+      </c>
+      <c r="I31" s="2">
+        <f t="shared" si="1"/>
+        <v>0.46466944444444441</v>
+      </c>
+      <c r="J31" s="2">
+        <f t="shared" si="1"/>
+        <v>18851.290000000005</v>
+      </c>
+      <c r="K31" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4721777777777767</v>
+      </c>
+      <c r="L31">
+        <v>2.2925</v>
+      </c>
+      <c r="M31" s="2">
+        <f t="shared" si="2"/>
+        <v>5.2555562499999997</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1.4750000000000001</v>
+      </c>
+      <c r="C32" s="2">
+        <v>3.5216666666666669</v>
+      </c>
+      <c r="D32" s="2">
+        <v>134.08333333333329</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2.078333333333334</v>
+      </c>
+      <c r="F32" s="2">
+        <v>63.611111111111107</v>
+      </c>
+      <c r="G32" s="2">
+        <v>52.9</v>
+      </c>
+      <c r="H32" s="2">
+        <f t="shared" si="1"/>
+        <v>2.1756250000000001</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" si="1"/>
+        <v>12.402136111111114</v>
+      </c>
+      <c r="J32" s="2">
+        <f t="shared" si="1"/>
+        <v>17978.340277777766</v>
+      </c>
+      <c r="K32" s="2">
+        <f t="shared" si="1"/>
+        <v>4.3194694444444472</v>
+      </c>
+      <c r="L32">
+        <v>5.1806666666666663</v>
+      </c>
+      <c r="M32" s="2">
+        <f t="shared" si="2"/>
+        <v>26.839307111111108</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.64666666666666672</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1.84</v>
+      </c>
+      <c r="D33" s="2">
+        <v>116.8333333333333</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1.8166666666666671</v>
+      </c>
+      <c r="F33" s="2">
+        <v>67.083333333333329</v>
+      </c>
+      <c r="G33" s="2">
+        <v>54.99</v>
+      </c>
+      <c r="H33" s="2">
+        <f t="shared" si="1"/>
+        <v>0.41817777777777787</v>
+      </c>
+      <c r="I33" s="2">
+        <f t="shared" si="1"/>
+        <v>3.3856000000000002</v>
+      </c>
+      <c r="J33" s="2">
+        <f t="shared" si="1"/>
+        <v>13650.02777777777</v>
+      </c>
+      <c r="K33" s="2">
+        <f t="shared" si="1"/>
+        <v>3.3002777777777794</v>
+      </c>
+      <c r="L33">
+        <v>4.5996666666666668</v>
+      </c>
+      <c r="M33" s="2">
+        <f t="shared" si="2"/>
+        <v>21.156933444444444</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1.3866666666666669</v>
+      </c>
+      <c r="D34" s="2">
+        <v>125.4166666666667</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1.845</v>
+      </c>
+      <c r="F34" s="2">
+        <v>66.180555555555557</v>
+      </c>
+      <c r="G34" s="2">
+        <v>54.44</v>
+      </c>
+      <c r="H34" s="2">
+        <f t="shared" si="1"/>
+        <v>0.20250000000000001</v>
+      </c>
+      <c r="I34" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9228444444444452</v>
+      </c>
+      <c r="J34" s="2">
+        <f t="shared" si="1"/>
+        <v>15729.340277777786</v>
+      </c>
+      <c r="K34" s="2">
+        <f t="shared" si="1"/>
+        <v>3.4040249999999999</v>
+      </c>
+      <c r="L34">
+        <v>4.418333333333333</v>
+      </c>
+      <c r="M34" s="2">
+        <f t="shared" si="2"/>
+        <v>19.521669444444441</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.1183333333333333</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.53666666666666663</v>
+      </c>
+      <c r="D35" s="2">
+        <v>182.15</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>35.902777777777779</v>
+      </c>
+      <c r="G35" s="2">
+        <v>36.81</v>
+      </c>
+      <c r="H35" s="2">
+        <f t="shared" si="1"/>
+        <v>1.400277777777777E-2</v>
+      </c>
+      <c r="I35" s="2">
+        <f t="shared" si="1"/>
+        <v>0.28801111111111105</v>
+      </c>
+      <c r="J35" s="2">
+        <f t="shared" si="1"/>
+        <v>33178.622500000005</v>
+      </c>
+      <c r="K35" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>2.4148333333333332</v>
+      </c>
+      <c r="M35" s="2">
+        <f t="shared" si="2"/>
+        <v>5.831420027777777</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1.1166666666666669</v>
+      </c>
+      <c r="C36" s="2">
+        <v>3.3583333333333329</v>
+      </c>
+      <c r="D36" s="2">
+        <v>135.3833333333333</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1.5549999999999999</v>
+      </c>
+      <c r="F36" s="2">
+        <v>48.194444444444443</v>
+      </c>
+      <c r="G36" s="2">
+        <v>43.97</v>
+      </c>
+      <c r="H36" s="2">
+        <f t="shared" si="1"/>
+        <v>1.2469444444444451</v>
+      </c>
+      <c r="I36" s="2">
+        <f t="shared" si="1"/>
+        <v>11.278402777777774</v>
+      </c>
+      <c r="J36" s="2">
+        <f t="shared" si="1"/>
+        <v>18328.646944444434</v>
+      </c>
+      <c r="K36" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4180249999999996</v>
+      </c>
+      <c r="L36">
+        <v>5.2380000000000004</v>
+      </c>
+      <c r="M36" s="2">
+        <f t="shared" si="2"/>
+        <v>27.436644000000005</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2.3266666666666671</v>
+      </c>
+      <c r="C37" s="2">
+        <v>3.5016666666666669</v>
+      </c>
+      <c r="D37" s="2">
+        <v>114.68333333333329</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="F37" s="2">
+        <v>64.097222222222229</v>
+      </c>
+      <c r="G37" s="2">
+        <v>53.19</v>
+      </c>
+      <c r="H37" s="2">
+        <f t="shared" si="1"/>
+        <v>5.4133777777777796</v>
+      </c>
+      <c r="I37" s="2">
+        <f t="shared" si="1"/>
+        <v>12.261669444444447</v>
+      </c>
+      <c r="J37" s="2">
+        <f t="shared" si="1"/>
+        <v>13152.266944444436</v>
+      </c>
+      <c r="K37" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3104</v>
+      </c>
+      <c r="L37">
+        <v>7.6448333333333336</v>
+      </c>
+      <c r="M37" s="2">
+        <f t="shared" si="2"/>
+        <v>58.443476694444449</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="2">
+        <v>1.958333333333333</v>
+      </c>
+      <c r="C38" s="2">
+        <v>4.2216666666666667</v>
+      </c>
+      <c r="D38" s="2">
+        <v>132.23333333333329</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1.4116666666666671</v>
+      </c>
+      <c r="F38" s="2">
+        <v>65.972222222222229</v>
+      </c>
+      <c r="G38" s="2">
+        <v>54.31</v>
+      </c>
+      <c r="H38" s="2">
+        <f t="shared" si="1"/>
+        <v>3.8350694444444433</v>
+      </c>
+      <c r="I38" s="2">
+        <f t="shared" si="1"/>
+        <v>17.822469444444444</v>
+      </c>
+      <c r="J38" s="2">
+        <f t="shared" si="1"/>
+        <v>17485.654444444433</v>
+      </c>
+      <c r="K38" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9928027777777788</v>
+      </c>
+      <c r="L38">
+        <v>6.6663333333333332</v>
+      </c>
+      <c r="M38" s="2">
+        <f t="shared" si="2"/>
+        <v>44.440000111111111</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
         <v>1</v>
       </c>
     </row>
